--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\betty\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3903DFD7-A770-46A4-884B-737FE7C46779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C14F159-F709-4477-BBEA-0FA45AC9353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FBB7BF38-EA19-4D44-B585-EBEF107DA81E}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{FBB7BF38-EA19-4D44-B585-EBEF107DA81E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="home work 1" sheetId="1" r:id="rId1"/>
+    <sheet name="store summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>store</t>
   </si>
@@ -78,6 +79,9 @@
   </si>
   <si>
     <t>store L</t>
+  </si>
+  <si>
+    <t>The over all average sales across the stores are in the mid to high 40 it showing that the most stores perform at similar level. when store H is included, the average increases because it has much higher value than the others. this makes the data more spread out, while removing store H makes the values more tightly grouped. Most stores have similar sales so the data without store H is more consistent.</t>
   </si>
 </sst>
 </file>
@@ -606,4 +610,19 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6713BE-44BB-446C-944A-53B5BDEF4368}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>